--- a/final_data_pipeline/output/325110longform_elec_options_nowhp.xlsx
+++ b/final_data_pipeline/output/325110longform_elec_options_nowhp.xlsx
@@ -645,7 +645,7 @@
         <v>62</v>
       </c>
       <c r="I2">
-        <v>10</v>
+        <v>12.67039049919483</v>
       </c>
       <c r="J2">
         <v>8000</v>
@@ -660,10 +660,10 @@
         <v>169.4098799338086</v>
       </c>
       <c r="N2">
-        <v>1.025288461538461</v>
+        <v>1.03592820319873</v>
       </c>
       <c r="O2">
-        <v>1.0563</v>
+        <v>1.067704754529766</v>
       </c>
       <c r="P2">
         <v>0.02117623499172607</v>
@@ -698,7 +698,7 @@
         <v>63</v>
       </c>
       <c r="I3">
-        <v>10</v>
+        <v>12.67039049919483</v>
       </c>
       <c r="J3">
         <v>8000</v>
@@ -745,7 +745,7 @@
         <v>63</v>
       </c>
       <c r="I4">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="J4">
         <v>8000</v>
@@ -792,7 +792,7 @@
         <v>62</v>
       </c>
       <c r="I5">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="J5">
         <v>8000</v>
@@ -807,10 +807,10 @@
         <v>32995.30490400347</v>
       </c>
       <c r="N5">
-        <v>1.025288461538461</v>
+        <v>0.9939102066179896</v>
       </c>
       <c r="O5">
-        <v>1.0563</v>
+        <v>1.022720671292561</v>
       </c>
       <c r="P5">
         <v>4.124413113000434</v>
@@ -845,7 +845,7 @@
         <v>63</v>
       </c>
       <c r="I6">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="J6">
         <v>8000</v>
@@ -2115,7 +2115,7 @@
         <v>63</v>
       </c>
       <c r="I32">
-        <v>10</v>
+        <v>20.68981481481483</v>
       </c>
       <c r="J32">
         <v>8000</v>
@@ -2162,7 +2162,7 @@
         <v>62</v>
       </c>
       <c r="I33">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="J33">
         <v>8000</v>
@@ -2177,10 +2177,10 @@
         <v>651265.6796054139</v>
       </c>
       <c r="N33">
-        <v>1.025288461538461</v>
+        <v>1.064821081830791</v>
       </c>
       <c r="O33">
-        <v>1.0563</v>
+        <v>1.098722912453048</v>
       </c>
       <c r="P33">
         <v>81.40820995067673</v>
@@ -2215,7 +2215,7 @@
         <v>63</v>
       </c>
       <c r="I34">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="J34">
         <v>8000</v>
@@ -2262,7 +2262,7 @@
         <v>62</v>
       </c>
       <c r="I35">
-        <v>10</v>
+        <v>20.68981481481483</v>
       </c>
       <c r="J35">
         <v>8000</v>
@@ -2277,10 +2277,10 @@
         <v>77758.08985627412</v>
       </c>
       <c r="N35">
-        <v>1.025288461538461</v>
+        <v>1.069250338898071</v>
       </c>
       <c r="O35">
-        <v>1.0563</v>
+        <v>1.103484165522044</v>
       </c>
       <c r="P35">
         <v>9.719761232034266</v>
@@ -2315,7 +2315,7 @@
         <v>63</v>
       </c>
       <c r="I36">
-        <v>10</v>
+        <v>20.68981481481483</v>
       </c>
       <c r="J36">
         <v>8000</v>
@@ -2944,7 +2944,7 @@
         <v>63</v>
       </c>
       <c r="I49">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="J49">
         <v>8000</v>
@@ -3038,7 +3038,7 @@
         <v>63</v>
       </c>
       <c r="I51">
-        <v>10</v>
+        <v>20.22222222222222</v>
       </c>
       <c r="J51">
         <v>8000</v>
